--- a/Documents/Product Catalog/Home/Living Room Furniture.xlsx
+++ b/Documents/Product Catalog/Home/Living Room Furniture.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Talukder Furniture\Documents\Product Catalog\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="d:\By Raj\Talukder Furniture\Documents\Product Catalog\Home\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9768CFE1-ADBF-46BF-A0A5-08B45FEF1158}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A1A065-BA01-4CCD-92A9-12FF39D98BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="397" uniqueCount="164">
   <si>
     <t>Talukder Furniture Ltd.</t>
   </si>
@@ -790,6 +790,12 @@
   </si>
   <si>
     <t>Double Seater Sofa</t>
+  </si>
+  <si>
+    <t>পদ্ম Showcase</t>
+  </si>
+  <si>
+    <t>শিল্পিক Showcase</t>
   </si>
 </sst>
 </file>
@@ -6229,7 +6235,7 @@
         <v>131</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="D32" s="8"/>
       <c r="E32" s="26" t="s">
@@ -6281,7 +6287,7 @@
         <v>140</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>132</v>
+        <v>163</v>
       </c>
       <c r="D33" s="8"/>
       <c r="E33" s="26" t="s">
